--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,29 +637,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -875,29 +875,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车08:15，减去该车自身同类时段历史终点停站中位数23分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1113,29 +1113,29 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1237,24 +1237,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±10分钟</t>
+          <t>07:11采样：该车到重点站唐陆公路顾家浜路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1556,24 +1556,24 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1586,34 +1586,34 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,47 +1627,880 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>92.0</t>
         </is>
       </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>8/9</t>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -994,29 +994,29 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车08:15，减去该车自身同类时段历史终点停站中位数23分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1118,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1232,29 +1232,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:11采样：该车到重点站唐陆公路顾家浜路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1351,27 +1351,31 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1462,29 +1470,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±12分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1494,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1518,12 +1526,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1533,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1586,26 +1594,22 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1642,7 +1646,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1652,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1700,29 +1704,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1756,12 +1760,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1771,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1824,24 +1828,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±13分钟</t>
+          <t>08:21采样：该车到重点站博兴路东陆路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,12 +1879,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1900,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1943,26 +1947,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 46分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2062,24 +2062,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±9分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2181,19 +2181,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2300,19 +2300,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2389,24 +2389,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2419,24 +2419,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±9分钟</t>
+          <t>08:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2460,47 +2460,999 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 29分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站德川路华夏东路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>2/13</t>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1589,27 +1589,31 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,12 +1645,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1671,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1823,29 +1827,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站博兴路东陆路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,12 +1883,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1894,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1942,27 +1946,31 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 46分钟</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1970,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,37 +2002,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2062,24 +2070,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>同车下一次反向发车09:35，减去该车自身同类时段历史终点停站中位数18分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2118,7 +2126,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2128,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2176,29 +2184,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2232,12 +2240,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2247,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2295,24 +2303,24 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2327,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2351,12 +2359,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2366,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2422,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2431,12 +2439,12 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2446,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2470,12 +2478,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2500,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2533,29 +2541,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 29分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2565,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,12 +2597,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2604,17 +2612,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2657,26 +2665,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站德川路华夏东路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 17分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2713,7 +2717,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2733,7 +2737,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2776,19 +2780,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站佳林路金高路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2832,7 +2836,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2852,12 +2856,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2895,24 +2899,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±14分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路春雅路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,7 +2955,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2971,12 +2975,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3014,24 +3018,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±6分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路锦绣东路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,7 +3074,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3090,7 +3094,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3133,24 +3137,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路创新路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,7 +3193,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3209,12 +3213,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3252,19 +3256,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站长岛路台儿庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3279,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,7 +3312,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3333,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3371,24 +3375,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>09:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3398,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,32 +3431,742 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>80.5</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2546,24 +2546,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2660,27 +2660,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 17分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2716,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2727,17 +2731,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2775,24 +2779,24 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站佳林路金高路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2835,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2846,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2894,29 +2898,29 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路春雅路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±11分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,12 +2954,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2965,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3013,29 +3017,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路锦绣东路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,12 +3073,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3084,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3132,29 +3136,29 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路创新路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3188,12 +3192,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3213,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3251,24 +3255,24 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站长岛路台儿庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3283,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,12 +3311,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3322,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3370,29 +3374,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±9分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3402,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,12 +3430,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3441,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3489,27 +3493,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3517,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3549,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3561,12 +3569,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3604,29 +3612,29 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3636,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3668,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3685,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3728,24 +3736,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+          <t>10:21采样：该车到重点站德川路华夏东路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3755,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,7 +3792,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3794,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3847,24 +3855,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站唐陆公路川桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3874,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,7 +3911,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3923,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3966,19 +3974,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站唐陆公路龙东大道 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3993,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,7 +4030,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4042,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4055,24 +4063,24 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4085,24 +4093,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+          <t>10:21采样：该车到重点站唐陆公路川桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4112,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,47 +4134,995 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站新川路华东路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3731,24 +3731,24 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站德川路华夏东路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3850,29 +3850,29 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站唐陆公路川桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站唐陆公路龙东大道 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4088,29 +4088,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站唐陆公路川桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4207,29 +4207,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站新川路华东路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4326,29 +4326,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4450,19 +4450,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 24分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4570,21 +4570,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:11采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4592,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,12 +4612,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4631,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4684,24 +4680,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>11:21采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4711,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,7 +4736,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4760,7 +4756,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4803,19 +4799,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>11:21采样：该车到重点站新德西路德翔路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4830,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,7 +4855,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4879,12 +4875,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4927,19 +4923,19 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+          <t>11:21采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4949,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,12 +4969,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4998,12 +4994,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5011,24 +5007,24 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5041,34 +5037,34 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>11:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5082,47 +5078,761 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>68分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4445,27 +4445,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 24分钟</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4473,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4501,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4522,7 +4526,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4560,27 +4564,31 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:11采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4588,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4620,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4637,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4675,29 +4683,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4707,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4739,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4756,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4794,24 +4802,24 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站新德西路德翔路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4826,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,12 +4858,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4865,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4918,26 +4926,22 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:51采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,7 +4978,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4994,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5032,29 +5036,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,12 +5092,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5113,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5151,29 +5155,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5183,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,12 +5211,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5222,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5270,29 +5274,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,12 +5330,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5351,7 +5355,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5394,26 +5398,22 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:22采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:19</t>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5460,22 +5460,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5513,19 +5513,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±5分钟</t>
+          <t>12:22采样：该车到重点站唐陆公路川桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5644,7 +5644,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
+          <t>12:22采样：该车到重点站唐陆公路龙东大道 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>12:22采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,32 +5807,746 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="Y46" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>80.2</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>66分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数66分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5041,24 +5041,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5279,24 +5279,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5393,27 +5393,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:22采样，终点ETA 44分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:19</t>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,12 +5449,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5470,7 +5474,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5508,29 +5512,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12:22采样：该车到重点站唐陆公路川桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5540,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,12 +5568,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5589,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5627,12 +5631,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5644,7 +5648,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12:22采样：该车到重点站唐陆公路龙东大道 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5687,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5698,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5746,29 +5750,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:22采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,12 +5806,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5827,7 +5831,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5870,26 +5874,22 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:11采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5984,29 +5984,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数66分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>13:21采样：该车到重点站东陆路金海路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6227,24 +6227,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>13:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,6 +6546,478 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>67分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>68分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
           <t>2/14</t>
         </is>
       </c>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,17 +4397,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5886,10 +5886,14 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:11采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5925,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5951,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5989,24 +5993,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6016,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6103,29 +6107,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站东陆路金海路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6135,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,12 +6163,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6184,12 +6188,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6226,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -6232,19 +6236,19 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,12 +6282,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6293,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6341,29 +6345,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6373,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,12 +6401,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6422,7 +6426,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6470,21 +6474,17 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:01采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6531,17 +6531,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6584,22 +6584,26 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>14:01采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -6607,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6635,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6651,12 +6655,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6699,19 +6703,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>14:01采样：该车到重点站新德西路德翔路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6755,7 +6759,7 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6775,12 +6779,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6898,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7022,6 +7026,363 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6231,12 +6231,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6464,27 +6464,31 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:01采样，终点ETA 44分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,12 +6520,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6541,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6583,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6596,12 +6600,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6611,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,12 +6639,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6703,26 +6707,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站新德西路德翔路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,22 +6754,22 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6822,19 +6822,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±5分钟</t>
+          <t>14:21采样：该车到重点站唐陆公路川桥路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6941,19 +6941,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数68分钟估算，约±5分钟</t>
+          <t>14:21采样：该车到重点站唐陆公路龙东大道 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7268,24 +7268,24 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7298,34 +7298,34 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,22 +7364,260 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>3/14</t>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6350,24 +6350,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6469,24 +6469,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,27 +6702,31 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:21采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6758,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6774,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6817,29 +6821,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站唐陆公路川桥路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6849,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6873,12 +6877,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6898,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6936,29 +6940,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站唐陆公路龙东大道 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6968,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,12 +6996,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7007,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7055,29 +7059,29 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7087,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,12 +7115,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7136,12 +7140,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7174,29 +7178,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7206,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,12 +7234,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7245,22 +7249,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7298,24 +7302,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±10分钟</t>
+          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数14分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7325,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7353,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7364,22 +7368,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7417,24 +7421,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>15:21采样：该车到重点站东陆路金海路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7444,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7473,7 +7477,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7493,7 +7497,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7506,24 +7510,24 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7536,24 +7540,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>15:21采样：该车到重点站新川路妙境路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7563,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7577,45 +7581,878 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>15:21采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X60" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
         <is>
           <t>4/14</t>
         </is>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,17 +5226,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,17 +6178,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6826,24 +6826,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7064,24 +7064,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7183,24 +7183,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7297,29 +7297,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数14分钟，约±14分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -7433,12 +7433,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站东陆路金海路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7535,24 +7535,24 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站新川路妙境路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7654,29 +7654,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7892,29 +7892,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8016,24 +8016,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站德川路华夏东路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8254,24 +8254,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8343,24 +8343,24 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8373,34 +8373,34 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站新川路华东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8414,47 +8414,753 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>67分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>4/14</t>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,17 +5107,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,22 +6535,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,14 +6773,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,17 +7249,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,22 +7487,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,14 +7725,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7790,12 +7790,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,22 +7963,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8011,29 +8011,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8082,22 +8082,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8130,29 +8130,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站德川路华夏东路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8201,22 +8201,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8249,29 +8249,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8368,29 +8368,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站新川路华东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8439,22 +8439,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8487,24 +8487,24 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8611,26 +8611,22 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8638,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,12 +8658,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8677,22 +8673,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8807,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8845,19 +8841,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 47分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
@@ -8868,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8897,7 +8893,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8922,7 +8918,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8960,19 +8956,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±5分钟</t>
+          <t>17:02采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8987,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9016,7 +9012,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9036,12 +9032,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9079,19 +9075,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站东陆路金海路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -9106,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9135,32 +9131,1091 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数99分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>14/14</t>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,22 +4516,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,22 +6535,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,22 +7130,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,22 +7487,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,22 +7606,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8201,22 +8201,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8373,24 +8373,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8492,19 +8492,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8616,17 +8616,21 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8634,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,12 +8662,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8683,12 +8687,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8721,27 +8725,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8749,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,37 +8781,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8836,27 +8844,31 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8864,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,37 +8900,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8951,29 +8963,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:02采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8983,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,12 +9019,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9022,22 +9034,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9070,29 +9082,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站东陆路金海路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9102,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,12 +9138,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9141,17 +9153,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9189,29 +9201,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9221,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,12 +9257,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9260,22 +9272,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9308,27 +9320,31 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -9336,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,37 +9376,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9423,29 +9439,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9455,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,12 +9495,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9504,12 +9520,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9547,19 +9563,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数99分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站德川路华夏东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9574,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9603,7 +9619,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9613,22 +9629,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9743,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9781,19 +9797,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±5分钟</t>
+          <t>18:11采样：该车到重点站唐陆公路顾家浜路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9808,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9837,7 +9853,7 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9857,12 +9873,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9905,14 +9921,14 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9927,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9956,7 +9972,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9976,12 +9992,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10091,12 +10107,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10104,24 +10120,24 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10134,24 +10150,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 40分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10161,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10190,32 +10206,853 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y85" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z85" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA85" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>9/14</t>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,22 +7249,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,22 +7725,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,22 +7963,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8439,22 +8439,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8682,17 +8682,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9444,12 +9444,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -9568,19 +9568,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站德川路华夏东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9677,27 +9677,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9705,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9729,37 +9733,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9797,26 +9801,22 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:11采样：该车到重点站唐陆公路顾家浜路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:51采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9863,22 +9863,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9911,24 +9911,24 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9982,22 +9982,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10030,27 +10030,31 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10058,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,17 +10086,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10102,17 +10106,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10145,29 +10149,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 40分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10177,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10201,12 +10205,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10226,12 +10230,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10269,26 +10273,22 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10498,29 +10498,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10569,12 +10569,12 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10622,19 +10622,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10856,19 +10856,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>19:21采样：该车到重点站新德西路德翔路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10945,22 +10945,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10993,12 +10993,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11012,47 +11012,634 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>78.8</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>10/14</t>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8206,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9153,17 +9153,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10035,24 +10035,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10273,19 +10273,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 13分钟</t>
+          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 6分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10622,24 +10622,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站唐陆公路南曹路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10868,12 +10868,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站新德西路德翔路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>同车下一次反向发车20:30，减去该车自身同类时段历史终点停站中位数10分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11090,22 +11090,26 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>19:31采样：该车到重点站唐陆公路台桥路 ETA 41分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11113,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11137,17 +11141,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11157,17 +11161,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11347,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11396,7 +11400,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11466,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11585,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11639,7 +11643,126 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,17 +4521,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8201,22 +8201,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8439,22 +8439,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9629,22 +9629,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9753,17 +9753,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9863,22 +9863,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10388,19 +10388,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:41采样，终点ETA 15分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,17 +10435,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10455,17 +10455,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10617,29 +10617,29 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站唐陆公路南曹路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10673,12 +10673,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10736,27 +10736,31 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -10764,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10788,17 +10792,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10808,17 +10812,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10851,29 +10855,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车20:30，减去该车自身同类时段历史终点停站中位数10分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10883,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10907,12 +10911,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10932,12 +10936,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10970,27 +10974,31 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10998,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11022,17 +11030,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11042,17 +11050,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11085,29 +11093,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:31采样：该车到重点站唐陆公路台桥路 ETA 41分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11117,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11141,12 +11149,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11156,22 +11164,22 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11209,19 +11217,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 21分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
@@ -11232,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11256,17 +11264,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11276,12 +11284,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11336,12 +11344,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11351,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11380,7 +11388,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11405,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11443,24 +11451,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+          <t>20:21采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11470,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11499,7 +11507,7 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11509,22 +11517,22 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11570,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -11574,12 +11582,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+          <t>20:21采样：该车到重点站博兴路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11589,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11618,7 +11626,7 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11643,7 +11651,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11757,12 +11765,250 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11212,27 +11212,31 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11240,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,12 +11268,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11289,7 +11293,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11327,29 +11331,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11359,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11383,12 +11387,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11408,12 +11412,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11446,29 +11450,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11478,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11502,12 +11506,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11527,7 +11531,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11565,24 +11569,24 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -11597,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,12 +11625,12 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11646,12 +11650,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11689,26 +11693,22 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 24分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11808,19 +11808,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11939,12 +11939,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>21:21采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">

--- a/data/export/2026-09-17-182路.xlsx
+++ b/data/export/2026-09-17-182路.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -11698,17 +11698,21 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 24分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11716,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11740,12 +11744,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11765,7 +11769,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11803,29 +11807,29 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11835,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11859,12 +11863,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11884,7 +11888,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11927,26 +11931,22 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11978,12 +11978,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
